--- a/python_acoustic_capture/verification_10_pairs/dataset/indexes/speech_dataset.xlsx
+++ b/python_acoustic_capture/verification_10_pairs/dataset/indexes/speech_dataset.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="355">
   <si>
     <t>dataset_sample_id</t>
   </si>
@@ -113,7 +113,7 @@
     <t>source_run</t>
   </si>
   <si>
-    <t>20260812_224312_ten_pair_closed_loop_scene__simulated_closed_loop_10_pairs__verify10_0001_target_01_interferer_01_rep001</t>
+    <t>20260816_235217_ten_pair_closed_loop_scene__simulated_closed_loop_10_pairs__verify10_0001_target_01_interferer_01_rep001</t>
   </si>
   <si>
     <t>simulated_closed_loop_10_pairs__verify10_0001_target_01_interferer_01_rep001</t>
@@ -128,10 +128,13 @@
     <t>通过</t>
   </si>
   <si>
-    <t>audio/20260812_224312_ten_pair_closed_loop_scene/raw/sample_0001_rep_001_mixture_mics.wav</t>
-  </si>
-  <si>
-    <t>audio/20260812_224312_ten_pair_closed_loop_scene/raw/sample_0001_rep_001_target_only_mics.wav</t>
+    <t>audio/target-mixed/20260816_235217_ten_pair_closed_loop_scene/sample_0001_rep_001_mixture_mics.wav</t>
+  </si>
+  <si>
+    <t>audio/target-only/20260816_235217_ten_pair_closed_loop_scene/sample_0001_rep_001_target_only_mics.wav</t>
+  </si>
+  <si>
+    <t>audio/interferer-only/20260816_235217_ten_pair_closed_loop_scene/sample_0001_rep_001_interferer_only_mics.wav</t>
   </si>
   <si>
     <t>1,2</t>
@@ -143,187 +146,220 @@
     <t>verify_ten_supervised_pairs</t>
   </si>
   <si>
+    <t>simulated_room</t>
+  </si>
+  <si>
     <t>simulator</t>
   </si>
   <si>
+    <t>simulator_model</t>
+  </si>
+  <si>
     <t>simulator_headset</t>
   </si>
   <si>
     <t>fixed</t>
   </si>
   <si>
-    <t>|simulator|simulator_headset|fixed|fixed</t>
-  </si>
-  <si>
-    <t>5e32bc39d285fa14a0927cce2e9602a3cad999ad02e6ed9f4a018acb5172f43f</t>
-  </si>
-  <si>
-    <t>17ad838dd45af9e01d1ac429ae8af8d1d34d805cf401a4f75a07fd7705fbe1e8</t>
-  </si>
-  <si>
-    <t>E:\Code_Github\Tools-main\Tools-main\python_acoustic_capture\verification_10_pairs\runs\20260812_224312_ten_pair_closed_loop_scene</t>
-  </si>
-  <si>
-    <t>20260812_224312_ten_pair_closed_loop_scene__simulated_closed_loop_10_pairs__verify10_0002_target_02_interferer_02_rep001</t>
+    <t>simulated_room|simulator|simulator_model|simulator_headset|fixed|fixed</t>
+  </si>
+  <si>
+    <t>de4de33ca90d064da7d544d57c9c93c97268ee695118e9f983f7e1c8ccff0d1b</t>
+  </si>
+  <si>
+    <t>9bfa37a37e412b0603ad6963961e8442b23b877c5d689c89ef6db0ff690c3726</t>
+  </si>
+  <si>
+    <t>E:\Code_Github\Tools-main\Tools-main\python_acoustic_capture\verification_10_pairs\runs\20260816_235217_ten_pair_closed_loop_scene</t>
+  </si>
+  <si>
+    <t>20260816_235217_ten_pair_closed_loop_scene__simulated_closed_loop_10_pairs__verify10_0002_target_02_interferer_02_rep001</t>
   </si>
   <si>
     <t>simulated_closed_loop_10_pairs__verify10_0002_target_02_interferer_02_rep001</t>
   </si>
   <si>
-    <t>audio/20260812_224312_ten_pair_closed_loop_scene/raw/sample_0002_rep_001_mixture_mics.wav</t>
-  </si>
-  <si>
-    <t>audio/20260812_224312_ten_pair_closed_loop_scene/raw/sample_0002_rep_001_target_only_mics.wav</t>
-  </si>
-  <si>
-    <t>5a722ab0f91f85b638f37ec052a315eb09618132d7ce021dc4f42cc73b98cd79</t>
-  </si>
-  <si>
-    <t>c94e36f2ba8313ac94e832f5048fb8eab7ed294aa2e6fd996b14b186e168e628</t>
-  </si>
-  <si>
-    <t>20260812_224312_ten_pair_closed_loop_scene__simulated_closed_loop_10_pairs__verify10_0003_target_03_interferer_03_rep001</t>
+    <t>audio/target-mixed/20260816_235217_ten_pair_closed_loop_scene/sample_0002_rep_001_mixture_mics.wav</t>
+  </si>
+  <si>
+    <t>audio/target-only/20260816_235217_ten_pair_closed_loop_scene/sample_0002_rep_001_target_only_mics.wav</t>
+  </si>
+  <si>
+    <t>audio/interferer-only/20260816_235217_ten_pair_closed_loop_scene/sample_0002_rep_001_interferer_only_mics.wav</t>
+  </si>
+  <si>
+    <t>472f1c2d46a4c4b06eded9f5b54cd4d24d41561f1b4a6b85b880ea65cca0a0a6</t>
+  </si>
+  <si>
+    <t>1d0424219208ee5784a271e1d16ca82f7da6b0df5d212e68c2a6953626e921b4</t>
+  </si>
+  <si>
+    <t>20260816_235217_ten_pair_closed_loop_scene__simulated_closed_loop_10_pairs__verify10_0003_target_03_interferer_03_rep001</t>
   </si>
   <si>
     <t>simulated_closed_loop_10_pairs__verify10_0003_target_03_interferer_03_rep001</t>
   </si>
   <si>
-    <t>audio/20260812_224312_ten_pair_closed_loop_scene/raw/sample_0003_rep_001_mixture_mics.wav</t>
-  </si>
-  <si>
-    <t>audio/20260812_224312_ten_pair_closed_loop_scene/raw/sample_0003_rep_001_target_only_mics.wav</t>
-  </si>
-  <si>
-    <t>a37f11d873a05efbd7411cba0200afd9ceb66ddea20a7ee17affa2e9e3f14eef</t>
-  </si>
-  <si>
-    <t>4f1af2598325d976d10ca666c2cb303c80389ae32a1bab1cd4d6bc92cd49a537</t>
-  </si>
-  <si>
-    <t>20260812_224312_ten_pair_closed_loop_scene__simulated_closed_loop_10_pairs__verify10_0004_target_04_interferer_04_rep001</t>
+    <t>audio/target-mixed/20260816_235217_ten_pair_closed_loop_scene/sample_0003_rep_001_mixture_mics.wav</t>
+  </si>
+  <si>
+    <t>audio/target-only/20260816_235217_ten_pair_closed_loop_scene/sample_0003_rep_001_target_only_mics.wav</t>
+  </si>
+  <si>
+    <t>audio/interferer-only/20260816_235217_ten_pair_closed_loop_scene/sample_0003_rep_001_interferer_only_mics.wav</t>
+  </si>
+  <si>
+    <t>341d2f733d7c3fe27061a343b6b4a729ba4a1edd82dc2b9d9444fd7d912ee1cb</t>
+  </si>
+  <si>
+    <t>63977f4940524c0be14b79ac7982197ca9b568820143ad18744d0530e4b428b2</t>
+  </si>
+  <si>
+    <t>20260816_235217_ten_pair_closed_loop_scene__simulated_closed_loop_10_pairs__verify10_0004_target_04_interferer_04_rep001</t>
   </si>
   <si>
     <t>simulated_closed_loop_10_pairs__verify10_0004_target_04_interferer_04_rep001</t>
   </si>
   <si>
-    <t>audio/20260812_224312_ten_pair_closed_loop_scene/raw/sample_0004_rep_001_mixture_mics.wav</t>
-  </si>
-  <si>
-    <t>audio/20260812_224312_ten_pair_closed_loop_scene/raw/sample_0004_rep_001_target_only_mics.wav</t>
-  </si>
-  <si>
-    <t>871df0a418ba3ccfaa77988e44a4262aa07be61403a3915859342227c5bbce83</t>
-  </si>
-  <si>
-    <t>9151be4645971ddb5ab6797f13c51225ee4bf4429e8fa99c9ebcedde7c795dd6</t>
-  </si>
-  <si>
-    <t>20260812_224312_ten_pair_closed_loop_scene__simulated_closed_loop_10_pairs__verify10_0005_target_05_interferer_05_rep001</t>
+    <t>audio/target-mixed/20260816_235217_ten_pair_closed_loop_scene/sample_0004_rep_001_mixture_mics.wav</t>
+  </si>
+  <si>
+    <t>audio/target-only/20260816_235217_ten_pair_closed_loop_scene/sample_0004_rep_001_target_only_mics.wav</t>
+  </si>
+  <si>
+    <t>audio/interferer-only/20260816_235217_ten_pair_closed_loop_scene/sample_0004_rep_001_interferer_only_mics.wav</t>
+  </si>
+  <si>
+    <t>e01064ed759fa77bfc897425e27bf5a977ca3d9c59e43fd27e8758b770153185</t>
+  </si>
+  <si>
+    <t>99f337990948b8a696665bfcba45990afa7448fb9b77e59a1ca86e0c82f45692</t>
+  </si>
+  <si>
+    <t>20260816_235217_ten_pair_closed_loop_scene__simulated_closed_loop_10_pairs__verify10_0005_target_05_interferer_05_rep001</t>
   </si>
   <si>
     <t>simulated_closed_loop_10_pairs__verify10_0005_target_05_interferer_05_rep001</t>
   </si>
   <si>
-    <t>audio/20260812_224312_ten_pair_closed_loop_scene/raw/sample_0005_rep_001_mixture_mics.wav</t>
-  </si>
-  <si>
-    <t>audio/20260812_224312_ten_pair_closed_loop_scene/raw/sample_0005_rep_001_target_only_mics.wav</t>
-  </si>
-  <si>
-    <t>8f7e121d33927e30832f422bfdf54ba8ef47b3b9b90868808fa472f61d729734</t>
-  </si>
-  <si>
-    <t>0ede1e4b61213f1e454e0037d495e520c6ababea9dff8f2fbb3a4255fd771d3b</t>
-  </si>
-  <si>
-    <t>20260812_224312_ten_pair_closed_loop_scene__simulated_closed_loop_10_pairs__verify10_0006_target_06_interferer_06_rep001</t>
+    <t>audio/target-mixed/20260816_235217_ten_pair_closed_loop_scene/sample_0005_rep_001_mixture_mics.wav</t>
+  </si>
+  <si>
+    <t>audio/target-only/20260816_235217_ten_pair_closed_loop_scene/sample_0005_rep_001_target_only_mics.wav</t>
+  </si>
+  <si>
+    <t>audio/interferer-only/20260816_235217_ten_pair_closed_loop_scene/sample_0005_rep_001_interferer_only_mics.wav</t>
+  </si>
+  <si>
+    <t>d17e52ea2afb696565edebeda96fce5d43129b6a681fe18181fec9793972d319</t>
+  </si>
+  <si>
+    <t>fc45d35b4ca108b011fd8388a0137ad1dcc6ceefa8415198cdaeafc548a9599c</t>
+  </si>
+  <si>
+    <t>20260816_235217_ten_pair_closed_loop_scene__simulated_closed_loop_10_pairs__verify10_0006_target_06_interferer_06_rep001</t>
   </si>
   <si>
     <t>simulated_closed_loop_10_pairs__verify10_0006_target_06_interferer_06_rep001</t>
   </si>
   <si>
-    <t>audio/20260812_224312_ten_pair_closed_loop_scene/raw/sample_0006_rep_001_mixture_mics.wav</t>
-  </si>
-  <si>
-    <t>audio/20260812_224312_ten_pair_closed_loop_scene/raw/sample_0006_rep_001_target_only_mics.wav</t>
-  </si>
-  <si>
-    <t>4922c4fcf08ef3944ef886326ac7cfc690b0095aef4645e0138b47bfb071a769</t>
-  </si>
-  <si>
-    <t>a360e85be6ceea8808483920495f02cf77dfc70fa743f48347ced3a957d1fb49</t>
-  </si>
-  <si>
-    <t>20260812_224312_ten_pair_closed_loop_scene__simulated_closed_loop_10_pairs__verify10_0007_target_07_interferer_07_rep001</t>
+    <t>audio/target-mixed/20260816_235217_ten_pair_closed_loop_scene/sample_0006_rep_001_mixture_mics.wav</t>
+  </si>
+  <si>
+    <t>audio/target-only/20260816_235217_ten_pair_closed_loop_scene/sample_0006_rep_001_target_only_mics.wav</t>
+  </si>
+  <si>
+    <t>audio/interferer-only/20260816_235217_ten_pair_closed_loop_scene/sample_0006_rep_001_interferer_only_mics.wav</t>
+  </si>
+  <si>
+    <t>a0a07955984bf927debddb624468eefec399db0429ca8d90f816516db5c7448d</t>
+  </si>
+  <si>
+    <t>ad19c55b000dbeb644a31173a7f8692acee2d37b52eb957ba165a597f975337c</t>
+  </si>
+  <si>
+    <t>20260816_235217_ten_pair_closed_loop_scene__simulated_closed_loop_10_pairs__verify10_0007_target_07_interferer_07_rep001</t>
   </si>
   <si>
     <t>simulated_closed_loop_10_pairs__verify10_0007_target_07_interferer_07_rep001</t>
   </si>
   <si>
-    <t>audio/20260812_224312_ten_pair_closed_loop_scene/raw/sample_0007_rep_001_mixture_mics.wav</t>
-  </si>
-  <si>
-    <t>audio/20260812_224312_ten_pair_closed_loop_scene/raw/sample_0007_rep_001_target_only_mics.wav</t>
-  </si>
-  <si>
-    <t>5a86fd572408bc0736e7b88eb290699d569780709963d8f23d31fa50a9d5a5c7</t>
-  </si>
-  <si>
-    <t>500f6136a981006757916c187f6c75bdeff6e66e27aad291c515ba0939bb96f1</t>
-  </si>
-  <si>
-    <t>20260812_224312_ten_pair_closed_loop_scene__simulated_closed_loop_10_pairs__verify10_0008_target_08_interferer_08_rep001</t>
+    <t>audio/target-mixed/20260816_235217_ten_pair_closed_loop_scene/sample_0007_rep_001_mixture_mics.wav</t>
+  </si>
+  <si>
+    <t>audio/target-only/20260816_235217_ten_pair_closed_loop_scene/sample_0007_rep_001_target_only_mics.wav</t>
+  </si>
+  <si>
+    <t>audio/interferer-only/20260816_235217_ten_pair_closed_loop_scene/sample_0007_rep_001_interferer_only_mics.wav</t>
+  </si>
+  <si>
+    <t>3640d0c64af75c94b221046d83bebb755557728e0558b7d34f70684ad6fc5cea</t>
+  </si>
+  <si>
+    <t>8e9b65b537bb81e6e5f174db86f21d13ed7db4558afc7aae8e5b8200118cbb57</t>
+  </si>
+  <si>
+    <t>20260816_235217_ten_pair_closed_loop_scene__simulated_closed_loop_10_pairs__verify10_0008_target_08_interferer_08_rep001</t>
   </si>
   <si>
     <t>simulated_closed_loop_10_pairs__verify10_0008_target_08_interferer_08_rep001</t>
   </si>
   <si>
-    <t>audio/20260812_224312_ten_pair_closed_loop_scene/raw/sample_0008_rep_001_mixture_mics.wav</t>
-  </si>
-  <si>
-    <t>audio/20260812_224312_ten_pair_closed_loop_scene/raw/sample_0008_rep_001_target_only_mics.wav</t>
-  </si>
-  <si>
-    <t>e8b4d3a97ca6ec387dda61e8be17d798217c51d963f14d0410d090d7d05ac11e</t>
-  </si>
-  <si>
-    <t>76bf51e624a186b2e4770cadff6e6a9465d39f8fc4439a1758f8295f2a8555c0</t>
-  </si>
-  <si>
-    <t>20260812_224312_ten_pair_closed_loop_scene__simulated_closed_loop_10_pairs__verify10_0009_target_09_interferer_09_rep001</t>
+    <t>audio/target-mixed/20260816_235217_ten_pair_closed_loop_scene/sample_0008_rep_001_mixture_mics.wav</t>
+  </si>
+  <si>
+    <t>audio/target-only/20260816_235217_ten_pair_closed_loop_scene/sample_0008_rep_001_target_only_mics.wav</t>
+  </si>
+  <si>
+    <t>audio/interferer-only/20260816_235217_ten_pair_closed_loop_scene/sample_0008_rep_001_interferer_only_mics.wav</t>
+  </si>
+  <si>
+    <t>9b8c0ae209465913e84d6d7a5382666bb787a1b493360b2a41a827b546a8f9d0</t>
+  </si>
+  <si>
+    <t>a13efcba3cafaeb148ceb0373827d745251a3de335c70b45e72fed9d26fc5adc</t>
+  </si>
+  <si>
+    <t>20260816_235217_ten_pair_closed_loop_scene__simulated_closed_loop_10_pairs__verify10_0009_target_09_interferer_09_rep001</t>
   </si>
   <si>
     <t>simulated_closed_loop_10_pairs__verify10_0009_target_09_interferer_09_rep001</t>
   </si>
   <si>
-    <t>audio/20260812_224312_ten_pair_closed_loop_scene/raw/sample_0009_rep_001_mixture_mics.wav</t>
-  </si>
-  <si>
-    <t>audio/20260812_224312_ten_pair_closed_loop_scene/raw/sample_0009_rep_001_target_only_mics.wav</t>
-  </si>
-  <si>
-    <t>c02c79ffb0e2d95d492b1c041dfcb3d9e3bcbabe8c866ef6ea2aff4bdb5b4e4a</t>
-  </si>
-  <si>
-    <t>f483a9521c017c4a0f9220edcc29bd11f8c83667957dfd95351eef2125d2534c</t>
-  </si>
-  <si>
-    <t>20260812_224312_ten_pair_closed_loop_scene__simulated_closed_loop_10_pairs__verify10_0010_target_10_interferer_10_rep001</t>
+    <t>audio/target-mixed/20260816_235217_ten_pair_closed_loop_scene/sample_0009_rep_001_mixture_mics.wav</t>
+  </si>
+  <si>
+    <t>audio/target-only/20260816_235217_ten_pair_closed_loop_scene/sample_0009_rep_001_target_only_mics.wav</t>
+  </si>
+  <si>
+    <t>audio/interferer-only/20260816_235217_ten_pair_closed_loop_scene/sample_0009_rep_001_interferer_only_mics.wav</t>
+  </si>
+  <si>
+    <t>50d0895fb3fad1c843d92824fa20e670c0e17c2b8780fa96f38f862ac30ea45c</t>
+  </si>
+  <si>
+    <t>1a2bb6c221136a421b6b72a307650029fc85873f73c86ca6b63ff06e688b856e</t>
+  </si>
+  <si>
+    <t>20260816_235217_ten_pair_closed_loop_scene__simulated_closed_loop_10_pairs__verify10_0010_target_10_interferer_10_rep001</t>
   </si>
   <si>
     <t>simulated_closed_loop_10_pairs__verify10_0010_target_10_interferer_10_rep001</t>
   </si>
   <si>
-    <t>audio/20260812_224312_ten_pair_closed_loop_scene/raw/sample_0010_rep_001_mixture_mics.wav</t>
-  </si>
-  <si>
-    <t>audio/20260812_224312_ten_pair_closed_loop_scene/raw/sample_0010_rep_001_target_only_mics.wav</t>
-  </si>
-  <si>
-    <t>6fc3919e93292c6c650dda3f6df7f21bb5c1ba393a15945f157e87e6383e640e</t>
-  </si>
-  <si>
-    <t>72de4e4d2d9c956dbcbd2e6dccb420a156e2461b0125d762f073b85c9e2f514a</t>
+    <t>audio/target-mixed/20260816_235217_ten_pair_closed_loop_scene/sample_0010_rep_001_mixture_mics.wav</t>
+  </si>
+  <si>
+    <t>audio/target-only/20260816_235217_ten_pair_closed_loop_scene/sample_0010_rep_001_target_only_mics.wav</t>
+  </si>
+  <si>
+    <t>audio/interferer-only/20260816_235217_ten_pair_closed_loop_scene/sample_0010_rep_001_interferer_only_mics.wav</t>
+  </si>
+  <si>
+    <t>e78fb84ff911da1b9092689f03015770bb3e7e7c3bfa60f10a4ab1f1e36a3988</t>
+  </si>
+  <si>
+    <t>4016cfb77d8af33e821b1cb60b97c6379608baa1b39f39c4c803363b3ec85e8d</t>
   </si>
   <si>
     <t>run_id</t>
@@ -515,7 +551,7 @@
     <t>source_mixture_recording</t>
   </si>
   <si>
-    <t>20260812_224312_ten_pair_closed_loop_scene</t>
+    <t>20260816_235217_ten_pair_closed_loop_scene</t>
   </si>
   <si>
     <t>supervised_pair</t>
@@ -530,24 +566,33 @@
     <t>未启用</t>
   </si>
   <si>
+    <t>{"definition":"mixture_recording - (target_only_recording + interferer_only_recording)","interpretation":"quality-control only; real sequential acoustic captures are not exact source images","channels":[{"channel":1,"mixture_consistency_residual_db":-39.31909156795951,"mixture_consistency_correlation":0.99994151947877,"estimated_sir_db":10.327282736271087,"target_rms_dbfs":-23.243623764669277,"interferer_rms_dbfs":-33.57090650094036,"mixture_rms_dbfs":-22.858214678903895},{"channel":2,"mixture_consistency_residual_db":-39.01192195562083,"mixture_consistency_correlation":0.9999372326247293,"estimated_sir_db":10.326466174890548,"target_rms_dbfs":-23.620908498525594,"interferer_rms_dbfs":-33.94737467341614,"mixture_rms_dbfs":-23.23540551139552}],"residual_db_max":-39.01192195562083,"correlation_min":0.9999372326247293}</t>
+  </si>
+  <si>
+    <t>metrics/sample_0001_rep_001_paired_sequence_supervision_quality.json</t>
+  </si>
+  <si>
+    <t>single_stream_paired_sequence</t>
+  </si>
+  <si>
+    <t>same_source_samples+single_continuous_full_duplex_stream</t>
+  </si>
+  <si>
+    <t>E:\Code_Github\Tools-main\Tools-main\python_acoustic_capture\verification_10_pairs\sources\target\target_01.wav</t>
+  </si>
+  <si>
+    <t>E:\Code_Github\Tools-main\Tools-main\python_acoustic_capture\verification_10_pairs\sources\interferer\interferer_01.wav</t>
+  </si>
+  <si>
+    <t>{"1":"left","2":"right"}</t>
+  </si>
+  <si>
+    <t>standard</t>
+  </si>
+  <si>
     <t>{}</t>
   </si>
   <si>
-    <t>single_stream_paired_sequence</t>
-  </si>
-  <si>
-    <t>same_source_samples+single_continuous_full_duplex_stream</t>
-  </si>
-  <si>
-    <t>E:\Code_Github\Tools-main\Tools-main\python_acoustic_capture\verification_10_pairs\sources\target\target_01.wav</t>
-  </si>
-  <si>
-    <t>E:\Code_Github\Tools-main\Tools-main\python_acoustic_capture\verification_10_pairs\sources\interferer\interferer_01.wav</t>
-  </si>
-  <si>
-    <t>standard</t>
-  </si>
-  <si>
     <t>simulated_mouth</t>
   </si>
   <si>
@@ -563,6 +608,9 @@
     <t>references/sample_0001_rep_001_target_only_playback.wav</t>
   </si>
   <si>
+    <t>references/sample_0001_rep_001_interferer_only_playback.wav</t>
+  </si>
+  <si>
     <t>references/sample_0001_rep_001_mixture_playback.wav</t>
   </si>
   <si>
@@ -575,21 +623,30 @@
     <t>metrics/sample_0001_rep_001_paired_sequence_layout.json</t>
   </si>
   <si>
-    <t>{"target_only":"metrics/sample_0001_rep_001_target_only.json","mixture":"metrics/sample_0001_rep_001_mixture.json"}</t>
-  </si>
-  <si>
-    <t>{"project_id":"verify_ten_supervised_pairs","scene_id":"simulated_closed_loop_10_pairs","experiment_id":"simulated_closed_loop_10_pairs","artificial_head_id":"simulator","headset_unit_id":"simulator_headset","wearing_id":"fixed","boom_pose_id":"fixed","target":{"source_id":"simulated_mouth","position_id":"front"},"interferer":{"source_id":"simulated_interferer","position_id":"right"}}</t>
+    <t>{"target_only":"metrics/sample_0001_rep_001_target_only.json","interferer_only":"metrics/sample_0001_rep_001_interferer_only.json","mixture":"metrics/sample_0001_rep_001_mixture.json"}</t>
+  </si>
+  <si>
+    <t>{"project_id":"verify_ten_supervised_pairs","room_id":"simulated_room","scene_id":"simulated_closed_loop_10_pairs","experiment_id":"simulated_closed_loop_10_pairs","artificial_head_id":"simulator","headset_model_id":"simulator_model","headset_unit_id":"simulator_headset","wearing_id":"fixed","boom_pose_id":"fixed","microphone_1":"left","microphone_2":"right","target":{"source_id":"simulated_mouth","position_id":"front","azimuth_deg":0,"elevation_deg":0,"height_m":1.4,"distance_m":0.05},"interferer":{"source_id":"simulated_interferer","position_id":"right","azimuth_deg":90,"elevation_deg":0,"height_m":1.4,"distance_m":1.0}}</t>
   </si>
   <si>
     <t>raw/sample_0001_rep_001_target_only_mics.wav</t>
   </si>
   <si>
+    <t>raw/sample_0001_rep_001_interferer_only_mics.wav</t>
+  </si>
+  <si>
     <t>raw/sample_0001_rep_001_mixture_mics.wav</t>
   </si>
   <si>
     <t>verify10_0002_target_02_interferer_02</t>
   </si>
   <si>
+    <t>{"definition":"mixture_recording - (target_only_recording + interferer_only_recording)","interpretation":"quality-control only; real sequential acoustic captures are not exact source images","channels":[{"channel":1,"mixture_consistency_residual_db":-36.399589910144876,"mixture_consistency_correlation":0.9998854632172717,"estimated_sir_db":3.6977258578448478,"target_rms_dbfs":-27.3771010309002,"interferer_rms_dbfs":-31.074826888745047,"mixture_rms_dbfs":-25.82888938866569},{"channel":2,"mixture_consistency_residual_db":-35.9085959972858,"mixture_consistency_correlation":0.9998717556858926,"estimated_sir_db":3.6961333289371003,"target_rms_dbfs":-27.75531071128281,"interferer_rms_dbfs":-31.45144404021991,"mixture_rms_dbfs":-26.206781824051696}],"residual_db_max":-35.9085959972858,"correlation_min":0.9998717556858926}</t>
+  </si>
+  <si>
+    <t>metrics/sample_0002_rep_001_paired_sequence_supervision_quality.json</t>
+  </si>
+  <si>
     <t>E:\Code_Github\Tools-main\Tools-main\python_acoustic_capture\verification_10_pairs\sources\target\target_02.wav</t>
   </si>
   <si>
@@ -599,6 +656,9 @@
     <t>references/sample_0002_rep_001_target_only_playback.wav</t>
   </si>
   <si>
+    <t>references/sample_0002_rep_001_interferer_only_playback.wav</t>
+  </si>
+  <si>
     <t>references/sample_0002_rep_001_mixture_playback.wav</t>
   </si>
   <si>
@@ -611,18 +671,27 @@
     <t>metrics/sample_0002_rep_001_paired_sequence_layout.json</t>
   </si>
   <si>
-    <t>{"target_only":"metrics/sample_0002_rep_001_target_only.json","mixture":"metrics/sample_0002_rep_001_mixture.json"}</t>
+    <t>{"target_only":"metrics/sample_0002_rep_001_target_only.json","interferer_only":"metrics/sample_0002_rep_001_interferer_only.json","mixture":"metrics/sample_0002_rep_001_mixture.json"}</t>
   </si>
   <si>
     <t>raw/sample_0002_rep_001_target_only_mics.wav</t>
   </si>
   <si>
+    <t>raw/sample_0002_rep_001_interferer_only_mics.wav</t>
+  </si>
+  <si>
     <t>raw/sample_0002_rep_001_mixture_mics.wav</t>
   </si>
   <si>
     <t>verify10_0003_target_03_interferer_03</t>
   </si>
   <si>
+    <t>{"definition":"mixture_recording - (target_only_recording + interferer_only_recording)","interpretation":"quality-control only; real sequential acoustic captures are not exact source images","channels":[{"channel":1,"mixture_consistency_residual_db":-36.67099689574694,"mixture_consistency_correlation":0.9998924028639884,"estimated_sir_db":6.592383186828306,"target_rms_dbfs":-26.327056652683837,"interferer_rms_dbfs":-32.919439839512144,"mixture_rms_dbfs":-25.458579977984492},{"channel":2,"mixture_consistency_residual_db":-36.40797493399384,"mixture_consistency_correlation":0.9998856867895538,"estimated_sir_db":6.591903293646732,"target_rms_dbfs":-26.70400186959612,"interferer_rms_dbfs":-33.29590516324285,"mixture_rms_dbfs":-25.835633880798557}],"residual_db_max":-36.40797493399384,"correlation_min":0.9998856867895538}</t>
+  </si>
+  <si>
+    <t>metrics/sample_0003_rep_001_paired_sequence_supervision_quality.json</t>
+  </si>
+  <si>
     <t>E:\Code_Github\Tools-main\Tools-main\python_acoustic_capture\verification_10_pairs\sources\target\target_03.wav</t>
   </si>
   <si>
@@ -632,6 +701,9 @@
     <t>references/sample_0003_rep_001_target_only_playback.wav</t>
   </si>
   <si>
+    <t>references/sample_0003_rep_001_interferer_only_playback.wav</t>
+  </si>
+  <si>
     <t>references/sample_0003_rep_001_mixture_playback.wav</t>
   </si>
   <si>
@@ -644,18 +716,27 @@
     <t>metrics/sample_0003_rep_001_paired_sequence_layout.json</t>
   </si>
   <si>
-    <t>{"target_only":"metrics/sample_0003_rep_001_target_only.json","mixture":"metrics/sample_0003_rep_001_mixture.json"}</t>
+    <t>{"target_only":"metrics/sample_0003_rep_001_target_only.json","interferer_only":"metrics/sample_0003_rep_001_interferer_only.json","mixture":"metrics/sample_0003_rep_001_mixture.json"}</t>
   </si>
   <si>
     <t>raw/sample_0003_rep_001_target_only_mics.wav</t>
   </si>
   <si>
+    <t>raw/sample_0003_rep_001_interferer_only_mics.wav</t>
+  </si>
+  <si>
     <t>raw/sample_0003_rep_001_mixture_mics.wav</t>
   </si>
   <si>
     <t>verify10_0004_target_04_interferer_04</t>
   </si>
   <si>
+    <t>{"definition":"mixture_recording - (target_only_recording + interferer_only_recording)","interpretation":"quality-control only; real sequential acoustic captures are not exact source images","channels":[{"channel":1,"mixture_consistency_residual_db":-36.65260080004588,"mixture_consistency_correlation":0.9998919490681544,"estimated_sir_db":3.3017989896747824,"target_rms_dbfs":-27.270972074750233,"interferer_rms_dbfs":-30.57277106442502,"mixture_rms_dbfs":-25.59174263828343},{"channel":2,"mixture_consistency_residual_db":-36.52018506395792,"mixture_consistency_correlation":0.9998886011686079,"estimated_sir_db":3.3004887845750037,"target_rms_dbfs":-27.64896185483057,"interferer_rms_dbfs":-30.949450639405573,"mixture_rms_dbfs":-25.9692686848345}],"residual_db_max":-36.52018506395792,"correlation_min":0.9998886011686079}</t>
+  </si>
+  <si>
+    <t>metrics/sample_0004_rep_001_paired_sequence_supervision_quality.json</t>
+  </si>
+  <si>
     <t>E:\Code_Github\Tools-main\Tools-main\python_acoustic_capture\verification_10_pairs\sources\target\target_04.wav</t>
   </si>
   <si>
@@ -665,6 +746,9 @@
     <t>references/sample_0004_rep_001_target_only_playback.wav</t>
   </si>
   <si>
+    <t>references/sample_0004_rep_001_interferer_only_playback.wav</t>
+  </si>
+  <si>
     <t>references/sample_0004_rep_001_mixture_playback.wav</t>
   </si>
   <si>
@@ -677,18 +761,27 @@
     <t>metrics/sample_0004_rep_001_paired_sequence_layout.json</t>
   </si>
   <si>
-    <t>{"target_only":"metrics/sample_0004_rep_001_target_only.json","mixture":"metrics/sample_0004_rep_001_mixture.json"}</t>
+    <t>{"target_only":"metrics/sample_0004_rep_001_target_only.json","interferer_only":"metrics/sample_0004_rep_001_interferer_only.json","mixture":"metrics/sample_0004_rep_001_mixture.json"}</t>
   </si>
   <si>
     <t>raw/sample_0004_rep_001_target_only_mics.wav</t>
   </si>
   <si>
+    <t>raw/sample_0004_rep_001_interferer_only_mics.wav</t>
+  </si>
+  <si>
     <t>raw/sample_0004_rep_001_mixture_mics.wav</t>
   </si>
   <si>
     <t>verify10_0005_target_05_interferer_05</t>
   </si>
   <si>
+    <t>{"definition":"mixture_recording - (target_only_recording + interferer_only_recording)","interpretation":"quality-control only; real sequential acoustic captures are not exact source images","channels":[{"channel":1,"mixture_consistency_residual_db":-38.29749436689765,"mixture_consistency_correlation":0.999926011823087,"estimated_sir_db":9.197097270944848,"target_rms_dbfs":-24.647404299472832,"interferer_rms_dbfs":-33.84450157041768,"mixture_rms_dbfs":-24.17575658067383},{"channel":2,"mixture_consistency_residual_db":-38.257895016387664,"mixture_consistency_correlation":0.9999253334251785,"estimated_sir_db":9.191886357092606,"target_rms_dbfs":-25.029307415181886,"interferer_rms_dbfs":-34.22119377227449,"mixture_rms_dbfs":-24.557213601977523}],"residual_db_max":-38.257895016387664,"correlation_min":0.9999253334251785}</t>
+  </si>
+  <si>
+    <t>metrics/sample_0005_rep_001_paired_sequence_supervision_quality.json</t>
+  </si>
+  <si>
     <t>E:\Code_Github\Tools-main\Tools-main\python_acoustic_capture\verification_10_pairs\sources\target\target_05.wav</t>
   </si>
   <si>
@@ -698,6 +791,9 @@
     <t>references/sample_0005_rep_001_target_only_playback.wav</t>
   </si>
   <si>
+    <t>references/sample_0005_rep_001_interferer_only_playback.wav</t>
+  </si>
+  <si>
     <t>references/sample_0005_rep_001_mixture_playback.wav</t>
   </si>
   <si>
@@ -710,18 +806,27 @@
     <t>metrics/sample_0005_rep_001_paired_sequence_layout.json</t>
   </si>
   <si>
-    <t>{"target_only":"metrics/sample_0005_rep_001_target_only.json","mixture":"metrics/sample_0005_rep_001_mixture.json"}</t>
+    <t>{"target_only":"metrics/sample_0005_rep_001_target_only.json","interferer_only":"metrics/sample_0005_rep_001_interferer_only.json","mixture":"metrics/sample_0005_rep_001_mixture.json"}</t>
   </si>
   <si>
     <t>raw/sample_0005_rep_001_target_only_mics.wav</t>
   </si>
   <si>
+    <t>raw/sample_0005_rep_001_interferer_only_mics.wav</t>
+  </si>
+  <si>
     <t>raw/sample_0005_rep_001_mixture_mics.wav</t>
   </si>
   <si>
     <t>verify10_0006_target_06_interferer_06</t>
   </si>
   <si>
+    <t>{"definition":"mixture_recording - (target_only_recording + interferer_only_recording)","interpretation":"quality-control only; real sequential acoustic captures are not exact source images","channels":[{"channel":1,"mixture_consistency_residual_db":-40.33775932355165,"mixture_consistency_correlation":0.9999537459566049,"estimated_sir_db":6.028173459538316,"target_rms_dbfs":-23.273850219424347,"interferer_rms_dbfs":-29.30202367896266,"mixture_rms_dbfs":-22.31394309412942},{"channel":2,"mixture_consistency_residual_db":-40.299127987231145,"mixture_consistency_correlation":0.9999533304127513,"estimated_sir_db":6.027712185806619,"target_rms_dbfs":-23.651202542881002,"interferer_rms_dbfs":-29.678914728687616,"mixture_rms_dbfs":-22.691102958761338}],"residual_db_max":-40.299127987231145,"correlation_min":0.9999533304127513}</t>
+  </si>
+  <si>
+    <t>metrics/sample_0006_rep_001_paired_sequence_supervision_quality.json</t>
+  </si>
+  <si>
     <t>E:\Code_Github\Tools-main\Tools-main\python_acoustic_capture\verification_10_pairs\sources\target\target_06.wav</t>
   </si>
   <si>
@@ -731,6 +836,9 @@
     <t>references/sample_0006_rep_001_target_only_playback.wav</t>
   </si>
   <si>
+    <t>references/sample_0006_rep_001_interferer_only_playback.wav</t>
+  </si>
+  <si>
     <t>references/sample_0006_rep_001_mixture_playback.wav</t>
   </si>
   <si>
@@ -743,18 +851,27 @@
     <t>metrics/sample_0006_rep_001_paired_sequence_layout.json</t>
   </si>
   <si>
-    <t>{"target_only":"metrics/sample_0006_rep_001_target_only.json","mixture":"metrics/sample_0006_rep_001_mixture.json"}</t>
+    <t>{"target_only":"metrics/sample_0006_rep_001_target_only.json","interferer_only":"metrics/sample_0006_rep_001_interferer_only.json","mixture":"metrics/sample_0006_rep_001_mixture.json"}</t>
   </si>
   <si>
     <t>raw/sample_0006_rep_001_target_only_mics.wav</t>
   </si>
   <si>
+    <t>raw/sample_0006_rep_001_interferer_only_mics.wav</t>
+  </si>
+  <si>
     <t>raw/sample_0006_rep_001_mixture_mics.wav</t>
   </si>
   <si>
     <t>verify10_0007_target_07_interferer_07</t>
   </si>
   <si>
+    <t>{"definition":"mixture_recording - (target_only_recording + interferer_only_recording)","interpretation":"quality-control only; real sequential acoustic captures are not exact source images","channels":[{"channel":1,"mixture_consistency_residual_db":-39.619349804148804,"mixture_consistency_correlation":0.9999454235517387,"estimated_sir_db":11.79131142063632,"target_rms_dbfs":-23.319998296366453,"interferer_rms_dbfs":-35.11130971700277,"mixture_rms_dbfs":-23.052155238820305},{"channel":2,"mixture_consistency_residual_db":-39.4848406929206,"mixture_consistency_correlation":0.9999437071722889,"estimated_sir_db":11.787911360474666,"target_rms_dbfs":-23.70019629540023,"interferer_rms_dbfs":-35.48810765587489,"mixture_rms_dbfs":-23.432231158066763}],"residual_db_max":-39.4848406929206,"correlation_min":0.9999437071722889}</t>
+  </si>
+  <si>
+    <t>metrics/sample_0007_rep_001_paired_sequence_supervision_quality.json</t>
+  </si>
+  <si>
     <t>E:\Code_Github\Tools-main\Tools-main\python_acoustic_capture\verification_10_pairs\sources\target\target_07.wav</t>
   </si>
   <si>
@@ -764,6 +881,9 @@
     <t>references/sample_0007_rep_001_target_only_playback.wav</t>
   </si>
   <si>
+    <t>references/sample_0007_rep_001_interferer_only_playback.wav</t>
+  </si>
+  <si>
     <t>references/sample_0007_rep_001_mixture_playback.wav</t>
   </si>
   <si>
@@ -776,18 +896,27 @@
     <t>metrics/sample_0007_rep_001_paired_sequence_layout.json</t>
   </si>
   <si>
-    <t>{"target_only":"metrics/sample_0007_rep_001_target_only.json","mixture":"metrics/sample_0007_rep_001_mixture.json"}</t>
+    <t>{"target_only":"metrics/sample_0007_rep_001_target_only.json","interferer_only":"metrics/sample_0007_rep_001_interferer_only.json","mixture":"metrics/sample_0007_rep_001_mixture.json"}</t>
   </si>
   <si>
     <t>raw/sample_0007_rep_001_target_only_mics.wav</t>
   </si>
   <si>
+    <t>raw/sample_0007_rep_001_interferer_only_mics.wav</t>
+  </si>
+  <si>
     <t>raw/sample_0007_rep_001_mixture_mics.wav</t>
   </si>
   <si>
     <t>verify10_0008_target_08_interferer_08</t>
   </si>
   <si>
+    <t>{"definition":"mixture_recording - (target_only_recording + interferer_only_recording)","interpretation":"quality-control only; real sequential acoustic captures are not exact source images","channels":[{"channel":1,"mixture_consistency_residual_db":-40.15351439597259,"mixture_consistency_correlation":0.9999517396161571,"estimated_sir_db":6.246516337117446,"target_rms_dbfs":-23.151839596367722,"interferer_rms_dbfs":-29.39835593348517,"mixture_rms_dbfs":-22.23298950985557},{"channel":2,"mixture_consistency_residual_db":-40.07565104645616,"mixture_consistency_correlation":0.9999508670423517,"estimated_sir_db":6.244305851686525,"target_rms_dbfs":-23.53106806066354,"interferer_rms_dbfs":-29.775373912350066,"mixture_rms_dbfs":-22.611752642898967}],"residual_db_max":-40.07565104645616,"correlation_min":0.9999508670423517}</t>
+  </si>
+  <si>
+    <t>metrics/sample_0008_rep_001_paired_sequence_supervision_quality.json</t>
+  </si>
+  <si>
     <t>E:\Code_Github\Tools-main\Tools-main\python_acoustic_capture\verification_10_pairs\sources\target\target_08.wav</t>
   </si>
   <si>
@@ -797,6 +926,9 @@
     <t>references/sample_0008_rep_001_target_only_playback.wav</t>
   </si>
   <si>
+    <t>references/sample_0008_rep_001_interferer_only_playback.wav</t>
+  </si>
+  <si>
     <t>references/sample_0008_rep_001_mixture_playback.wav</t>
   </si>
   <si>
@@ -809,18 +941,27 @@
     <t>metrics/sample_0008_rep_001_paired_sequence_layout.json</t>
   </si>
   <si>
-    <t>{"target_only":"metrics/sample_0008_rep_001_target_only.json","mixture":"metrics/sample_0008_rep_001_mixture.json"}</t>
+    <t>{"target_only":"metrics/sample_0008_rep_001_target_only.json","interferer_only":"metrics/sample_0008_rep_001_interferer_only.json","mixture":"metrics/sample_0008_rep_001_mixture.json"}</t>
   </si>
   <si>
     <t>raw/sample_0008_rep_001_target_only_mics.wav</t>
   </si>
   <si>
+    <t>raw/sample_0008_rep_001_interferer_only_mics.wav</t>
+  </si>
+  <si>
     <t>raw/sample_0008_rep_001_mixture_mics.wav</t>
   </si>
   <si>
     <t>verify10_0009_target_09_interferer_09</t>
   </si>
   <si>
+    <t>{"definition":"mixture_recording - (target_only_recording + interferer_only_recording)","interpretation":"quality-control only; real sequential acoustic captures are not exact source images","channels":[{"channel":1,"mixture_consistency_residual_db":-35.76736943282174,"mixture_consistency_correlation":0.999867518776188,"estimated_sir_db":6.35030292408544,"target_rms_dbfs":-27.354326885490128,"interferer_rms_dbfs":-33.704629809575565,"mixture_rms_dbfs":-26.452733846004556},{"channel":2,"mixture_consistency_residual_db":-35.65184168375041,"mixture_consistency_correlation":0.9998639538932517,"estimated_sir_db":6.349426375305858,"target_rms_dbfs":-27.731537416033575,"interferer_rms_dbfs":-34.080963791339435,"mixture_rms_dbfs":-26.830025607347572}],"residual_db_max":-35.65184168375041,"correlation_min":0.9998639538932517}</t>
+  </si>
+  <si>
+    <t>metrics/sample_0009_rep_001_paired_sequence_supervision_quality.json</t>
+  </si>
+  <si>
     <t>E:\Code_Github\Tools-main\Tools-main\python_acoustic_capture\verification_10_pairs\sources\target\target_09.wav</t>
   </si>
   <si>
@@ -830,6 +971,9 @@
     <t>references/sample_0009_rep_001_target_only_playback.wav</t>
   </si>
   <si>
+    <t>references/sample_0009_rep_001_interferer_only_playback.wav</t>
+  </si>
+  <si>
     <t>references/sample_0009_rep_001_mixture_playback.wav</t>
   </si>
   <si>
@@ -842,18 +986,27 @@
     <t>metrics/sample_0009_rep_001_paired_sequence_layout.json</t>
   </si>
   <si>
-    <t>{"target_only":"metrics/sample_0009_rep_001_target_only.json","mixture":"metrics/sample_0009_rep_001_mixture.json"}</t>
+    <t>{"target_only":"metrics/sample_0009_rep_001_target_only.json","interferer_only":"metrics/sample_0009_rep_001_interferer_only.json","mixture":"metrics/sample_0009_rep_001_mixture.json"}</t>
   </si>
   <si>
     <t>raw/sample_0009_rep_001_target_only_mics.wav</t>
   </si>
   <si>
+    <t>raw/sample_0009_rep_001_interferer_only_mics.wav</t>
+  </si>
+  <si>
     <t>raw/sample_0009_rep_001_mixture_mics.wav</t>
   </si>
   <si>
     <t>verify10_0010_target_10_interferer_10</t>
   </si>
   <si>
+    <t>{"definition":"mixture_recording - (target_only_recording + interferer_only_recording)","interpretation":"quality-control only; real sequential acoustic captures are not exact source images","channels":[{"channel":1,"mixture_consistency_residual_db":-37.84379345194286,"mixture_consistency_correlation":0.9999178658747345,"estimated_sir_db":4.000225185264664,"target_rms_dbfs":-25.91070691615618,"interferer_rms_dbfs":-29.91093210142084,"mixture_rms_dbfs":-24.458171979416505},{"channel":2,"mixture_consistency_residual_db":-37.51891954140044,"mixture_consistency_correlation":0.9999114853729923,"estimated_sir_db":3.998880088641098,"target_rms_dbfs":-26.288680883383904,"interferer_rms_dbfs":-30.287560972025002,"mixture_rms_dbfs":-24.835708610604147}],"residual_db_max":-37.51891954140044,"correlation_min":0.9999114853729923}</t>
+  </si>
+  <si>
+    <t>metrics/sample_0010_rep_001_paired_sequence_supervision_quality.json</t>
+  </si>
+  <si>
     <t>E:\Code_Github\Tools-main\Tools-main\python_acoustic_capture\verification_10_pairs\sources\target\target_10.wav</t>
   </si>
   <si>
@@ -863,6 +1016,9 @@
     <t>references/sample_0010_rep_001_target_only_playback.wav</t>
   </si>
   <si>
+    <t>references/sample_0010_rep_001_interferer_only_playback.wav</t>
+  </si>
+  <si>
     <t>references/sample_0010_rep_001_mixture_playback.wav</t>
   </si>
   <si>
@@ -875,12 +1031,15 @@
     <t>metrics/sample_0010_rep_001_paired_sequence_layout.json</t>
   </si>
   <si>
-    <t>{"target_only":"metrics/sample_0010_rep_001_target_only.json","mixture":"metrics/sample_0010_rep_001_mixture.json"}</t>
+    <t>{"target_only":"metrics/sample_0010_rep_001_target_only.json","interferer_only":"metrics/sample_0010_rep_001_interferer_only.json","mixture":"metrics/sample_0010_rep_001_mixture.json"}</t>
   </si>
   <si>
     <t>raw/sample_0010_rep_001_target_only_mics.wav</t>
   </si>
   <si>
+    <t>raw/sample_0010_rep_001_interferer_only_mics.wav</t>
+  </si>
+  <si>
     <t>raw/sample_0010_rep_001_mixture_mics.wav</t>
   </si>
   <si>
@@ -893,7 +1052,7 @@
     <t>sample_count</t>
   </si>
   <si>
-    <t>2026-08-12T14:43:12.632356+00:00</t>
+    <t>2026-08-16T15:52:17.996358+00:00</t>
   </si>
   <si>
     <t>completed</t>
@@ -1406,61 +1565,71 @@
       <c r="G2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H2" s="2"/>
+      <c r="H2" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="I2" s="2">
         <v>16000</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K2" s="2">
         <v>0.32</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="N2" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="O2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="P2" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="Q2" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
       <c r="V2" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="W2" s="2"/>
       <c r="X2" s="2"/>
       <c r="Y2" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA2" s="2"/>
-      <c r="AB2" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="AA2" s="2">
+        <v>-39.01192195562083</v>
+      </c>
+      <c r="AB2" s="2">
+        <v>0.9999372326247293</v>
+      </c>
       <c r="AC2" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:29">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>31</v>
@@ -1472,66 +1641,76 @@
         <v>33</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H3" s="2"/>
+        <v>52</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="I3" s="2">
         <v>16000</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K3" s="2">
         <v>0.32</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="N3" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="O3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="P3" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="Q3" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="T3" s="2"/>
       <c r="U3" s="2"/>
       <c r="V3" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="W3" s="2"/>
       <c r="X3" s="2"/>
       <c r="Y3" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA3" s="2"/>
-      <c r="AB3" s="2"/>
+        <v>55</v>
+      </c>
+      <c r="AA3" s="2">
+        <v>-35.9085959972858</v>
+      </c>
+      <c r="AB3" s="2">
+        <v>0.9998717556858926</v>
+      </c>
       <c r="AC3" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:29">
       <c r="A4" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>31</v>
@@ -1543,66 +1722,76 @@
         <v>33</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="H4" s="2"/>
+        <v>59</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="I4" s="2">
         <v>16000</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K4" s="2">
         <v>0.32</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="N4" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="O4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="P4" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="Q4" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
       <c r="V4" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="W4" s="2"/>
       <c r="X4" s="2"/>
       <c r="Y4" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="Z4" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA4" s="2"/>
-      <c r="AB4" s="2"/>
+        <v>62</v>
+      </c>
+      <c r="AA4" s="2">
+        <v>-36.40797493399384</v>
+      </c>
+      <c r="AB4" s="2">
+        <v>0.9998856867895538</v>
+      </c>
       <c r="AC4" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:29">
       <c r="A5" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>31</v>
@@ -1614,66 +1803,76 @@
         <v>33</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H5" s="2"/>
+        <v>66</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="I5" s="2">
         <v>16000</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K5" s="2">
         <v>0.32</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="N5" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="O5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="P5" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="Q5" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
       <c r="V5" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="W5" s="2"/>
       <c r="X5" s="2"/>
       <c r="Y5" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="Z5" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="AA5" s="2"/>
-      <c r="AB5" s="2"/>
+        <v>69</v>
+      </c>
+      <c r="AA5" s="2">
+        <v>-36.52018506395792</v>
+      </c>
+      <c r="AB5" s="2">
+        <v>0.9998886011686079</v>
+      </c>
       <c r="AC5" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:29">
       <c r="A6" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>31</v>
@@ -1685,66 +1884,76 @@
         <v>33</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H6" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="I6" s="2">
         <v>16000</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K6" s="2">
         <v>0.32</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="N6" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="O6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="P6" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="Q6" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
       <c r="V6" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="W6" s="2"/>
       <c r="X6" s="2"/>
       <c r="Y6" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA6" s="2"/>
-      <c r="AB6" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="AA6" s="2">
+        <v>-38.25789501638766</v>
+      </c>
+      <c r="AB6" s="2">
+        <v>0.9999253334251785</v>
+      </c>
       <c r="AC6" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:29">
       <c r="A7" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>31</v>
@@ -1756,66 +1965,76 @@
         <v>33</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H7" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>81</v>
+      </c>
       <c r="I7" s="2">
         <v>16000</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K7" s="2">
         <v>0.32</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="N7" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="O7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="P7" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="Q7" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
       <c r="V7" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="W7" s="2"/>
       <c r="X7" s="2"/>
       <c r="Y7" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="Z7" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AA7" s="2"/>
-      <c r="AB7" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="AA7" s="2">
+        <v>-40.29912798723115</v>
+      </c>
+      <c r="AB7" s="2">
+        <v>0.9999533304127513</v>
+      </c>
       <c r="AC7" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:29">
       <c r="A8" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>31</v>
@@ -1827,66 +2046,76 @@
         <v>33</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H8" s="2"/>
+        <v>87</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="I8" s="2">
         <v>16000</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K8" s="2">
         <v>0.32</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="N8" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="O8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="P8" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="Q8" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
       <c r="V8" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="W8" s="2"/>
       <c r="X8" s="2"/>
       <c r="Y8" s="2" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AA8" s="2"/>
-      <c r="AB8" s="2"/>
+        <v>90</v>
+      </c>
+      <c r="AA8" s="2">
+        <v>-39.4848406929206</v>
+      </c>
+      <c r="AB8" s="2">
+        <v>0.9999437071722889</v>
+      </c>
       <c r="AC8" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:29">
       <c r="A9" s="2" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>31</v>
@@ -1898,66 +2127,76 @@
         <v>33</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H9" s="2"/>
+        <v>94</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>95</v>
+      </c>
       <c r="I9" s="2">
         <v>16000</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K9" s="2">
         <v>0.32</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="O9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="P9" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="Q9" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
       <c r="V9" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="W9" s="2"/>
       <c r="X9" s="2"/>
       <c r="Y9" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA9" s="2"/>
-      <c r="AB9" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="AA9" s="2">
+        <v>-40.07565104645616</v>
+      </c>
+      <c r="AB9" s="2">
+        <v>0.9999508670423517</v>
+      </c>
       <c r="AC9" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:29">
       <c r="A10" s="2" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>31</v>
@@ -1969,66 +2208,76 @@
         <v>33</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H10" s="2"/>
+        <v>101</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>102</v>
+      </c>
       <c r="I10" s="2">
         <v>16000</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K10" s="2">
         <v>0.32</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="N10" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="O10" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="P10" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="Q10" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
       <c r="V10" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="W10" s="2"/>
       <c r="X10" s="2"/>
       <c r="Y10" s="2" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="Z10" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AA10" s="2"/>
-      <c r="AB10" s="2"/>
+        <v>104</v>
+      </c>
+      <c r="AA10" s="2">
+        <v>-35.65184168375041</v>
+      </c>
+      <c r="AB10" s="2">
+        <v>0.9998639538932517</v>
+      </c>
       <c r="AC10" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:29">
       <c r="A11" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>31</v>
@@ -2040,58 +2289,68 @@
         <v>33</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H11" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>109</v>
+      </c>
       <c r="I11" s="2">
         <v>16000</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K11" s="2">
         <v>0.32</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="N11" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="O11" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="P11" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="Q11" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
       <c r="V11" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="W11" s="2"/>
       <c r="X11" s="2"/>
       <c r="Y11" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="Z11" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA11" s="2"/>
-      <c r="AB11" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="AA11" s="2">
+        <v>-37.51891954140044</v>
+      </c>
+      <c r="AB11" s="2">
+        <v>0.9999114853729923</v>
+      </c>
       <c r="AC11" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -2116,46 +2375,46 @@
   <sheetData>
     <row r="1" spans="1:92">
       <c r="A1" s="1" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>26</v>
@@ -2164,37 +2423,37 @@
         <v>27</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>24</v>
@@ -2212,16 +2471,16 @@
         <v>9</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="AK1" s="1" t="s">
         <v>13</v>
@@ -2242,34 +2501,34 @@
         <v>18</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="AT1" s="1" t="s">
         <v>19</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="AX1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="BA1" s="1" t="s">
         <v>21</v>
@@ -2281,49 +2540,49 @@
         <v>23</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="BS1" s="1" t="s">
         <v>6</v>
@@ -2335,37 +2594,37 @@
         <v>5</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="CG1" s="1" t="s">
         <v>0</v>
@@ -2374,27 +2633,27 @@
         <v>28</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="CJ1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:92">
       <c r="A2" s="2" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>30</v>
@@ -2403,20 +2662,20 @@
         <v>30</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>31</v>
@@ -2428,22 +2687,28 @@
         <v>33</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="O2" s="2">
+        <v>-39.01192195562083</v>
+      </c>
+      <c r="P2" s="2">
+        <v>0.9999372326247293</v>
+      </c>
       <c r="Q2" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="R2" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>181</v>
+      </c>
       <c r="S2" s="2" t="s">
         <v>32</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="U2" s="2" t="s">
         <v>32</v>
@@ -2452,25 +2717,25 @@
         <v>32</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>166</v>
+        <v>32</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="Y2" s="2">
         <v>1</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="AD2" s="2">
         <v>0.32</v>
@@ -2479,7 +2744,7 @@
         <v>16000</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AG2" s="2">
         <v>1</v>
@@ -2493,25 +2758,29 @@
       <c r="AJ2" s="2">
         <v>-18</v>
       </c>
-      <c r="AK2" s="2"/>
+      <c r="AK2" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="AL2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM2" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="AM2" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="AN2" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="AS2" s="2"/>
       <c r="AT2" s="2"/>
@@ -2520,80 +2789,100 @@
       <c r="AW2" s="2"/>
       <c r="AX2" s="2"/>
       <c r="AY2" s="2" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="BB2" s="2"/>
       <c r="BC2" s="2"/>
       <c r="BD2" s="2"/>
       <c r="BE2" s="2"/>
       <c r="BF2" s="2" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="BH2" s="2"/>
-      <c r="BI2" s="2"/>
-      <c r="BJ2" s="2"/>
-      <c r="BK2" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="BH2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ2" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="BK2" s="2">
+        <v>0.05</v>
+      </c>
       <c r="BL2" s="2" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="BN2" s="2"/>
-      <c r="BO2" s="2"/>
-      <c r="BP2" s="2"/>
-      <c r="BQ2" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="BN2" s="2">
+        <v>90</v>
+      </c>
+      <c r="BO2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BP2" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="BQ2" s="2">
+        <v>1</v>
+      </c>
       <c r="BR2" s="2"/>
       <c r="BS2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="BT2" s="2"/>
+      <c r="BT2" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="BU2" s="2" t="s">
         <v>34</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="BW2" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="BW2" s="2" t="s">
+        <v>194</v>
+      </c>
       <c r="BX2" s="2" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="CB2" s="2">
         <v>400</v>
       </c>
       <c r="CC2" s="2">
-        <v>5920</v>
+        <v>11440</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="CF2" s="2"/>
       <c r="CG2" s="2" t="s">
         <v>29</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="CI2" s="2"/>
       <c r="CJ2" s="2" t="s">
@@ -2601,38 +2890,40 @@
       </c>
       <c r="CK2" s="2"/>
       <c r="CL2" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="CM2" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="CM2" s="2" t="s">
+        <v>202</v>
+      </c>
       <c r="CN2" s="2" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3" spans="1:92">
       <c r="A3" s="2" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>31</v>
@@ -2644,22 +2935,28 @@
         <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="O3" s="2">
+        <v>-35.9085959972858</v>
+      </c>
+      <c r="P3" s="2">
+        <v>0.9998717556858926</v>
+      </c>
       <c r="Q3" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="R3" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>206</v>
+      </c>
       <c r="S3" s="2" t="s">
         <v>32</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="U3" s="2" t="s">
         <v>32</v>
@@ -2668,25 +2965,25 @@
         <v>32</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>166</v>
+        <v>32</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="Y3" s="2">
         <v>1</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="AB3" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="AC3" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="AD3" s="2">
         <v>0.32</v>
@@ -2695,7 +2992,7 @@
         <v>16000</v>
       </c>
       <c r="AF3" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AG3" s="2">
         <v>1</v>
@@ -2709,25 +3006,29 @@
       <c r="AJ3" s="2">
         <v>-18</v>
       </c>
-      <c r="AK3" s="2"/>
+      <c r="AK3" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="AL3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM3" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="AN3" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AO3" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AP3" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AQ3" s="2" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="AR3" s="2" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="AS3" s="2"/>
       <c r="AT3" s="2"/>
@@ -2736,80 +3037,100 @@
       <c r="AW3" s="2"/>
       <c r="AX3" s="2"/>
       <c r="AY3" s="2" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="AZ3" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="BA3" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="BB3" s="2"/>
       <c r="BC3" s="2"/>
       <c r="BD3" s="2"/>
       <c r="BE3" s="2"/>
       <c r="BF3" s="2" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="BG3" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="BH3" s="2"/>
-      <c r="BI3" s="2"/>
-      <c r="BJ3" s="2"/>
-      <c r="BK3" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="BH3" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI3" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ3" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="BK3" s="2">
+        <v>0.05</v>
+      </c>
       <c r="BL3" s="2" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="BM3" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="BN3" s="2"/>
-      <c r="BO3" s="2"/>
-      <c r="BP3" s="2"/>
-      <c r="BQ3" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="BN3" s="2">
+        <v>90</v>
+      </c>
+      <c r="BO3" s="2">
+        <v>0</v>
+      </c>
+      <c r="BP3" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="BQ3" s="2">
+        <v>1</v>
+      </c>
       <c r="BR3" s="2"/>
       <c r="BS3" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="BT3" s="2"/>
+        <v>52</v>
+      </c>
+      <c r="BT3" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="BU3" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="BV3" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="BW3" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="BW3" s="2" t="s">
+        <v>210</v>
+      </c>
       <c r="BX3" s="2" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="BY3" s="2" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="BZ3" s="2" t="s">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="CA3" s="2" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="CB3" s="2">
         <v>400</v>
       </c>
       <c r="CC3" s="2">
-        <v>5920</v>
+        <v>11440</v>
       </c>
       <c r="CD3" s="2" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="CE3" s="2" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="CF3" s="2"/>
       <c r="CG3" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="CH3" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="CI3" s="2"/>
       <c r="CJ3" s="2" t="s">
@@ -2817,38 +3138,40 @@
       </c>
       <c r="CK3" s="2"/>
       <c r="CL3" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="CM3" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="CM3" s="2" t="s">
+        <v>217</v>
+      </c>
       <c r="CN3" s="2" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:92">
       <c r="A4" s="2" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>31</v>
@@ -2860,22 +3183,28 @@
         <v>33</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="O4" s="2">
+        <v>-36.40797493399384</v>
+      </c>
+      <c r="P4" s="2">
+        <v>0.9998856867895538</v>
+      </c>
       <c r="Q4" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="R4" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>221</v>
+      </c>
       <c r="S4" s="2" t="s">
         <v>32</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="U4" s="2" t="s">
         <v>32</v>
@@ -2884,25 +3213,25 @@
         <v>32</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>166</v>
+        <v>32</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="Y4" s="2">
         <v>1</v>
       </c>
       <c r="Z4" s="2" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="AA4" s="2" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="AB4" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AC4" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="AD4" s="2">
         <v>0.32</v>
@@ -2911,7 +3240,7 @@
         <v>16000</v>
       </c>
       <c r="AF4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AG4" s="2">
         <v>1</v>
@@ -2925,25 +3254,29 @@
       <c r="AJ4" s="2">
         <v>-18</v>
       </c>
-      <c r="AK4" s="2"/>
+      <c r="AK4" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="AL4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM4" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="AM4" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="AN4" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AO4" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AP4" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AQ4" s="2" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="AR4" s="2" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="AS4" s="2"/>
       <c r="AT4" s="2"/>
@@ -2952,80 +3285,100 @@
       <c r="AW4" s="2"/>
       <c r="AX4" s="2"/>
       <c r="AY4" s="2" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="AZ4" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="BA4" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="BB4" s="2"/>
       <c r="BC4" s="2"/>
       <c r="BD4" s="2"/>
       <c r="BE4" s="2"/>
       <c r="BF4" s="2" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="BG4" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="BH4" s="2"/>
-      <c r="BI4" s="2"/>
-      <c r="BJ4" s="2"/>
-      <c r="BK4" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="BH4" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI4" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ4" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="BK4" s="2">
+        <v>0.05</v>
+      </c>
       <c r="BL4" s="2" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="BM4" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="BN4" s="2"/>
-      <c r="BO4" s="2"/>
-      <c r="BP4" s="2"/>
-      <c r="BQ4" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="BN4" s="2">
+        <v>90</v>
+      </c>
+      <c r="BO4" s="2">
+        <v>0</v>
+      </c>
+      <c r="BP4" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="BQ4" s="2">
+        <v>1</v>
+      </c>
       <c r="BR4" s="2"/>
       <c r="BS4" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="BT4" s="2"/>
+        <v>59</v>
+      </c>
+      <c r="BT4" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="BU4" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="BV4" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="BW4" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="BW4" s="2" t="s">
+        <v>225</v>
+      </c>
       <c r="BX4" s="2" t="s">
-        <v>202</v>
+        <v>226</v>
       </c>
       <c r="BY4" s="2" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="BZ4" s="2" t="s">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="CA4" s="2" t="s">
-        <v>205</v>
+        <v>229</v>
       </c>
       <c r="CB4" s="2">
         <v>400</v>
       </c>
       <c r="CC4" s="2">
-        <v>5920</v>
+        <v>11440</v>
       </c>
       <c r="CD4" s="2" t="s">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="CE4" s="2" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="CF4" s="2"/>
       <c r="CG4" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="CH4" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="CI4" s="2"/>
       <c r="CJ4" s="2" t="s">
@@ -3033,38 +3386,40 @@
       </c>
       <c r="CK4" s="2"/>
       <c r="CL4" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="CM4" s="2"/>
+        <v>231</v>
+      </c>
+      <c r="CM4" s="2" t="s">
+        <v>232</v>
+      </c>
       <c r="CN4" s="2" t="s">
-        <v>208</v>
+        <v>233</v>
       </c>
     </row>
     <row r="5" spans="1:92">
       <c r="A5" s="2" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>31</v>
@@ -3076,22 +3431,28 @@
         <v>33</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="O5" s="2">
+        <v>-36.52018506395792</v>
+      </c>
+      <c r="P5" s="2">
+        <v>0.9998886011686079</v>
+      </c>
       <c r="Q5" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="R5" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>236</v>
+      </c>
       <c r="S5" s="2" t="s">
         <v>32</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="U5" s="2" t="s">
         <v>32</v>
@@ -3100,25 +3461,25 @@
         <v>32</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>166</v>
+        <v>32</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="Y5" s="2">
         <v>1</v>
       </c>
       <c r="Z5" s="2" t="s">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="AB5" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="AC5" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="AD5" s="2">
         <v>0.32</v>
@@ -3127,7 +3488,7 @@
         <v>16000</v>
       </c>
       <c r="AF5" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AG5" s="2">
         <v>1</v>
@@ -3141,25 +3502,29 @@
       <c r="AJ5" s="2">
         <v>-18</v>
       </c>
-      <c r="AK5" s="2"/>
+      <c r="AK5" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="AL5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM5" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="AM5" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="AN5" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AO5" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AP5" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AQ5" s="2" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="AR5" s="2" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="AS5" s="2"/>
       <c r="AT5" s="2"/>
@@ -3168,80 +3533,100 @@
       <c r="AW5" s="2"/>
       <c r="AX5" s="2"/>
       <c r="AY5" s="2" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="AZ5" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="BA5" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="BB5" s="2"/>
       <c r="BC5" s="2"/>
       <c r="BD5" s="2"/>
       <c r="BE5" s="2"/>
       <c r="BF5" s="2" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="BG5" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="BH5" s="2"/>
-      <c r="BI5" s="2"/>
-      <c r="BJ5" s="2"/>
-      <c r="BK5" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="BH5" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI5" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ5" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="BK5" s="2">
+        <v>0.05</v>
+      </c>
       <c r="BL5" s="2" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="BM5" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="BN5" s="2"/>
-      <c r="BO5" s="2"/>
-      <c r="BP5" s="2"/>
-      <c r="BQ5" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="BN5" s="2">
+        <v>90</v>
+      </c>
+      <c r="BO5" s="2">
+        <v>0</v>
+      </c>
+      <c r="BP5" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="BQ5" s="2">
+        <v>1</v>
+      </c>
       <c r="BR5" s="2"/>
       <c r="BS5" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="BT5" s="2"/>
+        <v>66</v>
+      </c>
+      <c r="BT5" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="BU5" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BV5" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="BW5" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="BW5" s="2" t="s">
+        <v>240</v>
+      </c>
       <c r="BX5" s="2" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="BY5" s="2" t="s">
-        <v>214</v>
+        <v>242</v>
       </c>
       <c r="BZ5" s="2" t="s">
-        <v>215</v>
+        <v>243</v>
       </c>
       <c r="CA5" s="2" t="s">
-        <v>216</v>
+        <v>244</v>
       </c>
       <c r="CB5" s="2">
         <v>400</v>
       </c>
       <c r="CC5" s="2">
-        <v>5920</v>
+        <v>11440</v>
       </c>
       <c r="CD5" s="2" t="s">
-        <v>217</v>
+        <v>245</v>
       </c>
       <c r="CE5" s="2" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="CF5" s="2"/>
       <c r="CG5" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="CH5" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="CI5" s="2"/>
       <c r="CJ5" s="2" t="s">
@@ -3249,38 +3634,40 @@
       </c>
       <c r="CK5" s="2"/>
       <c r="CL5" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="CM5" s="2"/>
+        <v>246</v>
+      </c>
+      <c r="CM5" s="2" t="s">
+        <v>247</v>
+      </c>
       <c r="CN5" s="2" t="s">
-        <v>219</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6" spans="1:92">
       <c r="A6" s="2" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>220</v>
+        <v>249</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>31</v>
@@ -3292,22 +3679,28 @@
         <v>33</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="O6" s="2">
+        <v>-38.25789501638766</v>
+      </c>
+      <c r="P6" s="2">
+        <v>0.9999253334251785</v>
+      </c>
       <c r="Q6" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="R6" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="S6" s="2" t="s">
         <v>32</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="U6" s="2" t="s">
         <v>32</v>
@@ -3316,25 +3709,25 @@
         <v>32</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>166</v>
+        <v>32</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="Y6" s="2">
         <v>1</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>221</v>
+        <v>252</v>
       </c>
       <c r="AA6" s="2" t="s">
-        <v>222</v>
+        <v>253</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="AC6" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="AD6" s="2">
         <v>0.32</v>
@@ -3343,7 +3736,7 @@
         <v>16000</v>
       </c>
       <c r="AF6" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AG6" s="2">
         <v>1</v>
@@ -3357,25 +3750,29 @@
       <c r="AJ6" s="2">
         <v>-18</v>
       </c>
-      <c r="AK6" s="2"/>
+      <c r="AK6" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="AL6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM6" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="AM6" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="AN6" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AO6" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AP6" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AQ6" s="2" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="AR6" s="2" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="AS6" s="2"/>
       <c r="AT6" s="2"/>
@@ -3384,80 +3781,100 @@
       <c r="AW6" s="2"/>
       <c r="AX6" s="2"/>
       <c r="AY6" s="2" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="AZ6" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="BA6" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="BB6" s="2"/>
       <c r="BC6" s="2"/>
       <c r="BD6" s="2"/>
       <c r="BE6" s="2"/>
       <c r="BF6" s="2" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="BG6" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="BH6" s="2"/>
-      <c r="BI6" s="2"/>
-      <c r="BJ6" s="2"/>
-      <c r="BK6" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="BH6" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI6" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ6" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="BK6" s="2">
+        <v>0.05</v>
+      </c>
       <c r="BL6" s="2" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="BM6" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="BN6" s="2"/>
-      <c r="BO6" s="2"/>
-      <c r="BP6" s="2"/>
-      <c r="BQ6" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="BN6" s="2">
+        <v>90</v>
+      </c>
+      <c r="BO6" s="2">
+        <v>0</v>
+      </c>
+      <c r="BP6" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="BQ6" s="2">
+        <v>1</v>
+      </c>
       <c r="BR6" s="2"/>
       <c r="BS6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="BT6" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="BT6" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="BU6" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="BV6" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="BW6" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="BW6" s="2" t="s">
+        <v>255</v>
+      </c>
       <c r="BX6" s="2" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="BY6" s="2" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="BZ6" s="2" t="s">
-        <v>226</v>
+        <v>258</v>
       </c>
       <c r="CA6" s="2" t="s">
-        <v>227</v>
+        <v>259</v>
       </c>
       <c r="CB6" s="2">
         <v>400</v>
       </c>
       <c r="CC6" s="2">
-        <v>5920</v>
+        <v>11440</v>
       </c>
       <c r="CD6" s="2" t="s">
-        <v>228</v>
+        <v>260</v>
       </c>
       <c r="CE6" s="2" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="CF6" s="2"/>
       <c r="CG6" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="CH6" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="CI6" s="2"/>
       <c r="CJ6" s="2" t="s">
@@ -3465,38 +3882,40 @@
       </c>
       <c r="CK6" s="2"/>
       <c r="CL6" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="CM6" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="CM6" s="2" t="s">
+        <v>262</v>
+      </c>
       <c r="CN6" s="2" t="s">
-        <v>230</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7" spans="1:92">
       <c r="A7" s="2" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>231</v>
+        <v>264</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>31</v>
@@ -3508,22 +3927,28 @@
         <v>33</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="O7" s="2">
+        <v>-40.29912798723115</v>
+      </c>
+      <c r="P7" s="2">
+        <v>0.9999533304127513</v>
+      </c>
       <c r="Q7" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="R7" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>266</v>
+      </c>
       <c r="S7" s="2" t="s">
         <v>32</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="U7" s="2" t="s">
         <v>32</v>
@@ -3532,25 +3957,25 @@
         <v>32</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>166</v>
+        <v>32</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="Y7" s="2">
         <v>1</v>
       </c>
       <c r="Z7" s="2" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
       <c r="AA7" s="2" t="s">
-        <v>233</v>
+        <v>268</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="AC7" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AD7" s="2">
         <v>0.32</v>
@@ -3559,7 +3984,7 @@
         <v>16000</v>
       </c>
       <c r="AF7" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AG7" s="2">
         <v>1</v>
@@ -3573,25 +3998,29 @@
       <c r="AJ7" s="2">
         <v>-18</v>
       </c>
-      <c r="AK7" s="2"/>
+      <c r="AK7" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="AL7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM7" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="AM7" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="AN7" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AO7" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AP7" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AQ7" s="2" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="AR7" s="2" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="AS7" s="2"/>
       <c r="AT7" s="2"/>
@@ -3600,80 +4029,100 @@
       <c r="AW7" s="2"/>
       <c r="AX7" s="2"/>
       <c r="AY7" s="2" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="AZ7" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="BA7" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="BB7" s="2"/>
       <c r="BC7" s="2"/>
       <c r="BD7" s="2"/>
       <c r="BE7" s="2"/>
       <c r="BF7" s="2" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="BG7" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="BH7" s="2"/>
-      <c r="BI7" s="2"/>
-      <c r="BJ7" s="2"/>
-      <c r="BK7" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="BH7" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI7" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ7" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="BK7" s="2">
+        <v>0.05</v>
+      </c>
       <c r="BL7" s="2" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="BM7" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="BN7" s="2"/>
-      <c r="BO7" s="2"/>
-      <c r="BP7" s="2"/>
-      <c r="BQ7" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="BN7" s="2">
+        <v>90</v>
+      </c>
+      <c r="BO7" s="2">
+        <v>0</v>
+      </c>
+      <c r="BP7" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="BQ7" s="2">
+        <v>1</v>
+      </c>
       <c r="BR7" s="2"/>
       <c r="BS7" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="BT7" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="BT7" s="2" t="s">
+        <v>81</v>
+      </c>
       <c r="BU7" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="BV7" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="BW7" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="BW7" s="2" t="s">
+        <v>270</v>
+      </c>
       <c r="BX7" s="2" t="s">
-        <v>235</v>
+        <v>271</v>
       </c>
       <c r="BY7" s="2" t="s">
-        <v>236</v>
+        <v>272</v>
       </c>
       <c r="BZ7" s="2" t="s">
-        <v>237</v>
+        <v>273</v>
       </c>
       <c r="CA7" s="2" t="s">
-        <v>238</v>
+        <v>274</v>
       </c>
       <c r="CB7" s="2">
         <v>400</v>
       </c>
       <c r="CC7" s="2">
-        <v>5920</v>
+        <v>11440</v>
       </c>
       <c r="CD7" s="2" t="s">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="CE7" s="2" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="CF7" s="2"/>
       <c r="CG7" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="CH7" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="CI7" s="2"/>
       <c r="CJ7" s="2" t="s">
@@ -3681,38 +4130,40 @@
       </c>
       <c r="CK7" s="2"/>
       <c r="CL7" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="CM7" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="CM7" s="2" t="s">
+        <v>277</v>
+      </c>
       <c r="CN7" s="2" t="s">
-        <v>241</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8" spans="1:92">
       <c r="A8" s="2" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>242</v>
+        <v>279</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>31</v>
@@ -3724,22 +4175,28 @@
         <v>33</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="O8" s="2">
+        <v>-39.4848406929206</v>
+      </c>
+      <c r="P8" s="2">
+        <v>0.9999437071722889</v>
+      </c>
       <c r="Q8" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="R8" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>281</v>
+      </c>
       <c r="S8" s="2" t="s">
         <v>32</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="U8" s="2" t="s">
         <v>32</v>
@@ -3748,25 +4205,25 @@
         <v>32</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>166</v>
+        <v>32</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="Y8" s="2">
         <v>1</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>243</v>
+        <v>282</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>244</v>
+        <v>283</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AC8" s="2" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AD8" s="2">
         <v>0.32</v>
@@ -3775,7 +4232,7 @@
         <v>16000</v>
       </c>
       <c r="AF8" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AG8" s="2">
         <v>1</v>
@@ -3789,25 +4246,29 @@
       <c r="AJ8" s="2">
         <v>-18</v>
       </c>
-      <c r="AK8" s="2"/>
+      <c r="AK8" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="AL8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM8" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="AM8" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="AN8" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AO8" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AP8" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AQ8" s="2" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="AR8" s="2" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="AS8" s="2"/>
       <c r="AT8" s="2"/>
@@ -3816,80 +4277,100 @@
       <c r="AW8" s="2"/>
       <c r="AX8" s="2"/>
       <c r="AY8" s="2" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="AZ8" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="BA8" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="BB8" s="2"/>
       <c r="BC8" s="2"/>
       <c r="BD8" s="2"/>
       <c r="BE8" s="2"/>
       <c r="BF8" s="2" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="BG8" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="BH8" s="2"/>
-      <c r="BI8" s="2"/>
-      <c r="BJ8" s="2"/>
-      <c r="BK8" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="BH8" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI8" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ8" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="BK8" s="2">
+        <v>0.05</v>
+      </c>
       <c r="BL8" s="2" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="BM8" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="BN8" s="2"/>
-      <c r="BO8" s="2"/>
-      <c r="BP8" s="2"/>
-      <c r="BQ8" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="BN8" s="2">
+        <v>90</v>
+      </c>
+      <c r="BO8" s="2">
+        <v>0</v>
+      </c>
+      <c r="BP8" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="BQ8" s="2">
+        <v>1</v>
+      </c>
       <c r="BR8" s="2"/>
       <c r="BS8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="BT8" s="2"/>
+        <v>87</v>
+      </c>
+      <c r="BT8" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="BU8" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="BV8" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="BW8" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="BW8" s="2" t="s">
+        <v>285</v>
+      </c>
       <c r="BX8" s="2" t="s">
-        <v>246</v>
+        <v>286</v>
       </c>
       <c r="BY8" s="2" t="s">
-        <v>247</v>
+        <v>287</v>
       </c>
       <c r="BZ8" s="2" t="s">
-        <v>248</v>
+        <v>288</v>
       </c>
       <c r="CA8" s="2" t="s">
-        <v>249</v>
+        <v>289</v>
       </c>
       <c r="CB8" s="2">
         <v>400</v>
       </c>
       <c r="CC8" s="2">
-        <v>5920</v>
+        <v>11440</v>
       </c>
       <c r="CD8" s="2" t="s">
-        <v>250</v>
+        <v>290</v>
       </c>
       <c r="CE8" s="2" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="CF8" s="2"/>
       <c r="CG8" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="CH8" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="CI8" s="2"/>
       <c r="CJ8" s="2" t="s">
@@ -3897,38 +4378,40 @@
       </c>
       <c r="CK8" s="2"/>
       <c r="CL8" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="CM8" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="CM8" s="2" t="s">
+        <v>292</v>
+      </c>
       <c r="CN8" s="2" t="s">
-        <v>252</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" spans="1:92">
       <c r="A9" s="2" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>253</v>
+        <v>294</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>31</v>
@@ -3940,22 +4423,28 @@
         <v>33</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="O9" s="2">
+        <v>-40.07565104645616</v>
+      </c>
+      <c r="P9" s="2">
+        <v>0.9999508670423517</v>
+      </c>
       <c r="Q9" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="R9" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>296</v>
+      </c>
       <c r="S9" s="2" t="s">
         <v>32</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="U9" s="2" t="s">
         <v>32</v>
@@ -3964,25 +4453,25 @@
         <v>32</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>166</v>
+        <v>32</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="Y9" s="2">
         <v>1</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>254</v>
+        <v>297</v>
       </c>
       <c r="AA9" s="2" t="s">
-        <v>255</v>
+        <v>298</v>
       </c>
       <c r="AB9" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="AC9" s="2" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AD9" s="2">
         <v>0.32</v>
@@ -3991,7 +4480,7 @@
         <v>16000</v>
       </c>
       <c r="AF9" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AG9" s="2">
         <v>1</v>
@@ -4005,25 +4494,29 @@
       <c r="AJ9" s="2">
         <v>-18</v>
       </c>
-      <c r="AK9" s="2"/>
+      <c r="AK9" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="AL9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM9" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="AM9" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="AN9" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AO9" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AP9" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AQ9" s="2" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="AR9" s="2" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="AS9" s="2"/>
       <c r="AT9" s="2"/>
@@ -4032,80 +4525,100 @@
       <c r="AW9" s="2"/>
       <c r="AX9" s="2"/>
       <c r="AY9" s="2" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="AZ9" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="BA9" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="BB9" s="2"/>
       <c r="BC9" s="2"/>
       <c r="BD9" s="2"/>
       <c r="BE9" s="2"/>
       <c r="BF9" s="2" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="BG9" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="BH9" s="2"/>
-      <c r="BI9" s="2"/>
-      <c r="BJ9" s="2"/>
-      <c r="BK9" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="BH9" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI9" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ9" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="BK9" s="2">
+        <v>0.05</v>
+      </c>
       <c r="BL9" s="2" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="BM9" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="BN9" s="2"/>
-      <c r="BO9" s="2"/>
-      <c r="BP9" s="2"/>
-      <c r="BQ9" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="BN9" s="2">
+        <v>90</v>
+      </c>
+      <c r="BO9" s="2">
+        <v>0</v>
+      </c>
+      <c r="BP9" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="BQ9" s="2">
+        <v>1</v>
+      </c>
       <c r="BR9" s="2"/>
       <c r="BS9" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="BT9" s="2"/>
+        <v>94</v>
+      </c>
+      <c r="BT9" s="2" t="s">
+        <v>95</v>
+      </c>
       <c r="BU9" s="2" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="BV9" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="BW9" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="BW9" s="2" t="s">
+        <v>300</v>
+      </c>
       <c r="BX9" s="2" t="s">
-        <v>257</v>
+        <v>301</v>
       </c>
       <c r="BY9" s="2" t="s">
-        <v>258</v>
+        <v>302</v>
       </c>
       <c r="BZ9" s="2" t="s">
-        <v>259</v>
+        <v>303</v>
       </c>
       <c r="CA9" s="2" t="s">
-        <v>260</v>
+        <v>304</v>
       </c>
       <c r="CB9" s="2">
         <v>400</v>
       </c>
       <c r="CC9" s="2">
-        <v>5920</v>
+        <v>11440</v>
       </c>
       <c r="CD9" s="2" t="s">
-        <v>261</v>
+        <v>305</v>
       </c>
       <c r="CE9" s="2" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="CF9" s="2"/>
       <c r="CG9" s="2" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="CH9" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="CI9" s="2"/>
       <c r="CJ9" s="2" t="s">
@@ -4113,38 +4626,40 @@
       </c>
       <c r="CK9" s="2"/>
       <c r="CL9" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="CM9" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="CM9" s="2" t="s">
+        <v>307</v>
+      </c>
       <c r="CN9" s="2" t="s">
-        <v>263</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10" spans="1:92">
       <c r="A10" s="2" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>264</v>
+        <v>309</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>31</v>
@@ -4156,22 +4671,28 @@
         <v>33</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="O10" s="2">
+        <v>-35.65184168375041</v>
+      </c>
+      <c r="P10" s="2">
+        <v>0.9998639538932517</v>
+      </c>
       <c r="Q10" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="R10" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>311</v>
+      </c>
       <c r="S10" s="2" t="s">
         <v>32</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="U10" s="2" t="s">
         <v>32</v>
@@ -4180,25 +4701,25 @@
         <v>32</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>166</v>
+        <v>32</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="Y10" s="2">
         <v>1</v>
       </c>
       <c r="Z10" s="2" t="s">
-        <v>265</v>
+        <v>312</v>
       </c>
       <c r="AA10" s="2" t="s">
-        <v>266</v>
+        <v>313</v>
       </c>
       <c r="AB10" s="2" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="AC10" s="2" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="AD10" s="2">
         <v>0.32</v>
@@ -4207,7 +4728,7 @@
         <v>16000</v>
       </c>
       <c r="AF10" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AG10" s="2">
         <v>1</v>
@@ -4221,25 +4742,29 @@
       <c r="AJ10" s="2">
         <v>-18</v>
       </c>
-      <c r="AK10" s="2"/>
+      <c r="AK10" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="AL10" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM10" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="AM10" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="AN10" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AO10" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AP10" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AQ10" s="2" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="AR10" s="2" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="AS10" s="2"/>
       <c r="AT10" s="2"/>
@@ -4248,80 +4773,100 @@
       <c r="AW10" s="2"/>
       <c r="AX10" s="2"/>
       <c r="AY10" s="2" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="AZ10" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="BA10" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="BB10" s="2"/>
       <c r="BC10" s="2"/>
       <c r="BD10" s="2"/>
       <c r="BE10" s="2"/>
       <c r="BF10" s="2" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="BG10" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="BH10" s="2"/>
-      <c r="BI10" s="2"/>
-      <c r="BJ10" s="2"/>
-      <c r="BK10" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="BH10" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI10" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ10" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="BK10" s="2">
+        <v>0.05</v>
+      </c>
       <c r="BL10" s="2" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="BM10" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="BN10" s="2"/>
-      <c r="BO10" s="2"/>
-      <c r="BP10" s="2"/>
-      <c r="BQ10" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="BN10" s="2">
+        <v>90</v>
+      </c>
+      <c r="BO10" s="2">
+        <v>0</v>
+      </c>
+      <c r="BP10" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="BQ10" s="2">
+        <v>1</v>
+      </c>
       <c r="BR10" s="2"/>
       <c r="BS10" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="BT10" s="2"/>
+        <v>101</v>
+      </c>
+      <c r="BT10" s="2" t="s">
+        <v>102</v>
+      </c>
       <c r="BU10" s="2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="BV10" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="BW10" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="BW10" s="2" t="s">
+        <v>315</v>
+      </c>
       <c r="BX10" s="2" t="s">
-        <v>268</v>
+        <v>316</v>
       </c>
       <c r="BY10" s="2" t="s">
-        <v>269</v>
+        <v>317</v>
       </c>
       <c r="BZ10" s="2" t="s">
-        <v>270</v>
+        <v>318</v>
       </c>
       <c r="CA10" s="2" t="s">
-        <v>271</v>
+        <v>319</v>
       </c>
       <c r="CB10" s="2">
         <v>400</v>
       </c>
       <c r="CC10" s="2">
-        <v>5920</v>
+        <v>11440</v>
       </c>
       <c r="CD10" s="2" t="s">
-        <v>272</v>
+        <v>320</v>
       </c>
       <c r="CE10" s="2" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="CF10" s="2"/>
       <c r="CG10" s="2" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="CH10" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="CI10" s="2"/>
       <c r="CJ10" s="2" t="s">
@@ -4329,38 +4874,40 @@
       </c>
       <c r="CK10" s="2"/>
       <c r="CL10" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="CM10" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="CM10" s="2" t="s">
+        <v>322</v>
+      </c>
       <c r="CN10" s="2" t="s">
-        <v>274</v>
+        <v>323</v>
       </c>
     </row>
     <row r="11" spans="1:92">
       <c r="A11" s="2" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>275</v>
+        <v>324</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>31</v>
@@ -4372,22 +4919,28 @@
         <v>33</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="O11" s="2">
+        <v>-37.51891954140044</v>
+      </c>
+      <c r="P11" s="2">
+        <v>0.9999114853729923</v>
+      </c>
       <c r="Q11" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="R11" s="2"/>
+        <v>325</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>326</v>
+      </c>
       <c r="S11" s="2" t="s">
         <v>32</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="U11" s="2" t="s">
         <v>32</v>
@@ -4396,25 +4949,25 @@
         <v>32</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>166</v>
+        <v>32</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="Y11" s="2">
         <v>1</v>
       </c>
       <c r="Z11" s="2" t="s">
-        <v>276</v>
+        <v>327</v>
       </c>
       <c r="AA11" s="2" t="s">
-        <v>277</v>
+        <v>328</v>
       </c>
       <c r="AB11" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="AC11" s="2" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="AD11" s="2">
         <v>0.32</v>
@@ -4423,7 +4976,7 @@
         <v>16000</v>
       </c>
       <c r="AF11" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AG11" s="2">
         <v>1</v>
@@ -4437,25 +4990,29 @@
       <c r="AJ11" s="2">
         <v>-18</v>
       </c>
-      <c r="AK11" s="2"/>
+      <c r="AK11" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="AL11" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM11" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="AM11" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="AN11" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AO11" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AP11" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AQ11" s="2" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="AR11" s="2" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="AS11" s="2"/>
       <c r="AT11" s="2"/>
@@ -4464,80 +5021,100 @@
       <c r="AW11" s="2"/>
       <c r="AX11" s="2"/>
       <c r="AY11" s="2" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="AZ11" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="BA11" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="BB11" s="2"/>
       <c r="BC11" s="2"/>
       <c r="BD11" s="2"/>
       <c r="BE11" s="2"/>
       <c r="BF11" s="2" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="BG11" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="BH11" s="2"/>
-      <c r="BI11" s="2"/>
-      <c r="BJ11" s="2"/>
-      <c r="BK11" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="BH11" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI11" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ11" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="BK11" s="2">
+        <v>0.05</v>
+      </c>
       <c r="BL11" s="2" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="BM11" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="BN11" s="2"/>
-      <c r="BO11" s="2"/>
-      <c r="BP11" s="2"/>
-      <c r="BQ11" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="BN11" s="2">
+        <v>90</v>
+      </c>
+      <c r="BO11" s="2">
+        <v>0</v>
+      </c>
+      <c r="BP11" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="BQ11" s="2">
+        <v>1</v>
+      </c>
       <c r="BR11" s="2"/>
       <c r="BS11" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="BT11" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="BT11" s="2" t="s">
+        <v>109</v>
+      </c>
       <c r="BU11" s="2" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="BV11" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="BW11" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="BW11" s="2" t="s">
+        <v>330</v>
+      </c>
       <c r="BX11" s="2" t="s">
-        <v>279</v>
+        <v>331</v>
       </c>
       <c r="BY11" s="2" t="s">
-        <v>280</v>
+        <v>332</v>
       </c>
       <c r="BZ11" s="2" t="s">
-        <v>281</v>
+        <v>333</v>
       </c>
       <c r="CA11" s="2" t="s">
-        <v>282</v>
+        <v>334</v>
       </c>
       <c r="CB11" s="2">
         <v>400</v>
       </c>
       <c r="CC11" s="2">
-        <v>5920</v>
+        <v>11440</v>
       </c>
       <c r="CD11" s="2" t="s">
-        <v>283</v>
+        <v>335</v>
       </c>
       <c r="CE11" s="2" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="CF11" s="2"/>
       <c r="CG11" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="CH11" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="CI11" s="2"/>
       <c r="CJ11" s="2" t="s">
@@ -4545,11 +5122,13 @@
       </c>
       <c r="CK11" s="2"/>
       <c r="CL11" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="CM11" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="CM11" s="2" t="s">
+        <v>337</v>
+      </c>
       <c r="CN11" s="2" t="s">
-        <v>285</v>
+        <v>338</v>
       </c>
     </row>
   </sheetData>
@@ -4568,10 +5147,10 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>286</v>
+        <v>339</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>11</v>
@@ -4580,10 +5159,10 @@
         <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>287</v>
+        <v>340</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>288</v>
+        <v>341</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>28</v>
@@ -4591,25 +5170,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>289</v>
+        <v>342</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>290</v>
+        <v>343</v>
       </c>
       <c r="F2" s="2">
         <v>10</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -4628,10 +5207,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>287</v>
+        <v>340</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>291</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -4639,7 +5218,7 @@
         <v>33</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>292</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -4659,12 +5238,12 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
-        <v>293</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>294</v>
+        <v>347</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -4672,7 +5251,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>295</v>
+        <v>348</v>
       </c>
       <c r="B4">
         <v>10</v>
@@ -4680,7 +5259,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>296</v>
+        <v>349</v>
       </c>
       <c r="B5">
         <v>10</v>
@@ -4688,7 +5267,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>297</v>
+        <v>350</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -4696,7 +5275,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>298</v>
+        <v>351</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -4704,7 +5283,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>299</v>
+        <v>352</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -4712,7 +5291,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>300</v>
+        <v>353</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -4720,7 +5299,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>301</v>
+        <v>354</v>
       </c>
       <c r="B10">
         <v>0</v>
